--- a/config/divergent-universe-generated/templates/DivergentUniverseReview.xlsx
+++ b/config/divergent-universe-generated/templates/DivergentUniverseReview.xlsx
@@ -52,7 +52,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>5468dadae234f4d9</t>
+    <t>ef1cc1687fc1f979</t>
   </si>
   <si>
     <t>#name</t>
@@ -127,13 +127,13 @@
     <t>string</t>
   </si>
   <si>
-    <t>enum&lt;DUOwnership&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;DUCoverageState&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;DUEvidenceQuality&gt;</t>
+    <t>enum&lt;DuOwnership&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;DuCoverageState&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;DuEvidenceQuality&gt;</t>
   </si>
   <si>
     <t>optional&lt;list&lt;ref&lt;DivergentUniverseSources.id&gt;&gt;&gt;</t>
@@ -184,7 +184,7 @@
     <t>DivergentUniverseMechanicRules</t>
   </si>
   <si>
-    <t>51cd3010a956361a</t>
+    <t>0b50460bb15c3f3a</t>
   </si>
   <si>
     <t>source_file_id</t>
@@ -217,7 +217,7 @@
     <t>DivergentUniverseSources</t>
   </si>
   <si>
-    <t>e726554b3484d994</t>
+    <t>45b5bcb9ce09c5b4</t>
   </si>
   <si>
     <t>repository</t>
@@ -241,7 +241,7 @@
     <t>DivergentUniverseCoverage</t>
   </si>
   <si>
-    <t>08db02bf88cbb71b</t>
+    <t>3e4023f6704a4a3b</t>
   </si>
   <si>
     <t>blocking_gap_ids</t>
@@ -265,7 +265,7 @@
     <t>DivergentUniverseResearchGaps</t>
   </si>
   <si>
-    <t>23a1229965dafda7</t>
+    <t>31e3579bd67b4607</t>
   </si>
   <si>
     <t>field</t>
@@ -286,7 +286,7 @@
     <t>DivergentUniverseSemanticFixtureFamilies</t>
   </si>
   <si>
-    <t>682d0d9b3729ec5e</t>
+    <t>3fde11670712167e</t>
   </si>
   <si>
     <t>minimum_cases</t>
@@ -298,7 +298,7 @@
     <t>DivergentUniverseReviewFixtures</t>
   </si>
   <si>
-    <t>b5d849af6b8e5a06</t>
+    <t>4c7d9ad7bbb800a6</t>
   </si>
   <si>
     <t>family_id</t>
@@ -322,7 +322,7 @@
     <t>DivergentUniverseReconciliationReceipts</t>
   </si>
   <si>
-    <t>b377e4372a28c611</t>
+    <t>3bcc7fa6d46e52b1</t>
   </si>
   <si>
     <t>row_locator</t>
@@ -340,7 +340,7 @@
     <t>DivergentUniverseManifest</t>
   </si>
   <si>
-    <t>0e87da4657f6b8fb</t>
+    <t>0efea6e4cb517e1b</t>
   </si>
   <si>
     <t>content_manifest_sha256</t>
@@ -355,7 +355,7 @@
     <t>DivergentUniversePackIndex</t>
   </si>
   <si>
-    <t>6ca35f435885b89b</t>
+    <t>f4cd7ce332ac7d3b</t>
   </si>
   <si>
     <t>pack_digest</t>
@@ -1172,14 +1172,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1547,14 +1547,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1984,14 +1984,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2402,14 +2402,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2812,14 +2812,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3216,14 +3216,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3577,14 +3577,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4000,14 +4000,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4403,14 +4403,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4780,14 +4780,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
